--- a/menu/the-great-invention-menu.xlsx
+++ b/menu/the-great-invention-menu.xlsx
@@ -438,7 +438,6 @@
       </c>
       <c r="B1" s="1" t="inlineStr"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -532,7 +531,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -890,7 +888,6 @@
       <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>saute</t>
@@ -922,7 +919,6 @@
       <c r="D3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>saute</t>
@@ -954,7 +950,6 @@
       <c r="D4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>saute</t>
@@ -986,7 +981,6 @@
       <c r="D5" t="n">
         <v>16</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1018,7 +1012,6 @@
       <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1050,7 +1043,6 @@
       <c r="D7" t="n">
         <v>2.5</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1080,9 +1072,8 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1114,7 +1105,6 @@
       <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1146,7 +1136,6 @@
       <c r="D10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1178,7 +1167,6 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1210,7 +1198,6 @@
       <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1242,7 +1229,6 @@
       <c r="D13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1274,7 +1260,6 @@
       <c r="D14" t="n">
         <v>8</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1306,7 +1291,6 @@
       <c r="D15" t="n">
         <v>9</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1338,7 +1322,6 @@
       <c r="D16" t="n">
         <v>11</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1370,7 +1353,6 @@
       <c r="D17" t="n">
         <v>12</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1402,7 +1384,6 @@
       <c r="D18" t="n">
         <v>13</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1434,7 +1415,6 @@
       <c r="D19" t="n">
         <v>11</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1466,7 +1446,6 @@
       <c r="D20" t="n">
         <v>13</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1498,7 +1477,6 @@
       <c r="D21" t="n">
         <v>13</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1514,12 +1492,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MY-SNP-KUHIT</t>
+          <t>MY-SNP-KUNYIT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Set Nasi Putih Daging Goreng Ku Hit</t>
+          <t>Set Nasi Putih Daging Goreng Kunyit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1530,7 +1508,6 @@
       <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1562,7 +1539,6 @@
       <c r="D23" t="n">
         <v>11</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1594,7 +1570,6 @@
       <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1626,7 +1601,6 @@
       <c r="D25" t="n">
         <v>13</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1658,7 +1632,6 @@
       <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1690,7 +1663,6 @@
       <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1722,7 +1694,6 @@
       <c r="D28" t="n">
         <v>12</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1754,7 +1725,6 @@
       <c r="D29" t="n">
         <v>13</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1786,7 +1756,6 @@
       <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1818,7 +1787,6 @@
       <c r="D31" t="n">
         <v>9</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1850,7 +1818,6 @@
       <c r="D32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1882,7 +1849,6 @@
       <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1914,7 +1880,6 @@
       <c r="D34" t="n">
         <v>12</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1946,7 +1911,6 @@
       <c r="D35" t="n">
         <v>9</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>saute</t>
@@ -1978,7 +1942,6 @@
       <c r="D36" t="n">
         <v>12</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2010,7 +1973,6 @@
       <c r="D37" t="n">
         <v>8</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2042,7 +2004,6 @@
       <c r="D38" t="n">
         <v>9</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2074,7 +2035,6 @@
       <c r="D39" t="n">
         <v>12</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2106,7 +2066,6 @@
       <c r="D40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2138,7 +2097,6 @@
       <c r="D41" t="n">
         <v>12</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2170,7 +2128,6 @@
       <c r="D42" t="n">
         <v>8</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2202,7 +2159,6 @@
       <c r="D43" t="n">
         <v>8</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2234,7 +2190,6 @@
       <c r="D44" t="n">
         <v>8</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2266,7 +2221,6 @@
       <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2298,7 +2252,6 @@
       <c r="D46" t="n">
         <v>9</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2330,7 +2283,6 @@
       <c r="D47" t="n">
         <v>9</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2362,7 +2314,6 @@
       <c r="D48" t="n">
         <v>9</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2394,7 +2345,6 @@
       <c r="D49" t="n">
         <v>13</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2426,7 +2376,6 @@
       <c r="D50" t="n">
         <v>11</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2458,7 +2407,6 @@
       <c r="D51" t="n">
         <v>13</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2490,7 +2438,6 @@
       <c r="D52" t="n">
         <v>13</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2522,7 +2469,6 @@
       <c r="D53" t="n">
         <v>12</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2554,7 +2500,6 @@
       <c r="D54" t="n">
         <v>11</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2586,7 +2531,6 @@
       <c r="D55" t="n">
         <v>12</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2618,7 +2562,6 @@
       <c r="D56" t="n">
         <v>13</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2650,7 +2593,6 @@
       <c r="D57" t="n">
         <v>10</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2682,7 +2624,6 @@
       <c r="D58" t="n">
         <v>12</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2714,7 +2655,6 @@
       <c r="D59" t="n">
         <v>13</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2746,7 +2686,6 @@
       <c r="D60" t="n">
         <v>11</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2778,7 +2717,6 @@
       <c r="D61" t="n">
         <v>9</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2810,7 +2748,6 @@
       <c r="D62" t="n">
         <v>9</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2842,7 +2779,6 @@
       <c r="D63" t="n">
         <v>9</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2874,7 +2810,6 @@
       <c r="D64" t="n">
         <v>9</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2906,7 +2841,6 @@
       <c r="D65" t="n">
         <v>7</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>saute</t>
@@ -2938,7 +2872,6 @@
       <c r="D66" t="n">
         <v>13.9</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>grill</t>
@@ -2970,7 +2903,6 @@
       <c r="D67" t="n">
         <v>13.9</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>grill</t>
@@ -3002,7 +2934,6 @@
       <c r="D68" t="n">
         <v>15.9</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>grill</t>
@@ -3034,7 +2965,6 @@
       <c r="D69" t="n">
         <v>16.9</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>grill</t>
@@ -3066,7 +2996,6 @@
       <c r="D70" t="n">
         <v>19.9</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>grill</t>
@@ -3098,7 +3027,6 @@
       <c r="D71" t="n">
         <v>15.9</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3130,7 +3058,6 @@
       <c r="D72" t="n">
         <v>10.9</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3162,7 +3089,6 @@
       <c r="D73" t="n">
         <v>12.9</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3194,7 +3120,6 @@
       <c r="D74" t="n">
         <v>14.9</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3226,7 +3151,6 @@
       <c r="D75" t="n">
         <v>18.9</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3258,7 +3182,6 @@
       <c r="D76" t="n">
         <v>13.9</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3290,7 +3213,6 @@
       <c r="D77" t="n">
         <v>12.9</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3322,7 +3244,6 @@
       <c r="D78" t="n">
         <v>11.9</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3354,7 +3275,6 @@
       <c r="D79" t="n">
         <v>13.9</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3386,7 +3306,6 @@
       <c r="D80" t="n">
         <v>18.9</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3418,7 +3337,6 @@
       <c r="D81" t="n">
         <v>6.9</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3450,7 +3368,6 @@
       <c r="D82" t="n">
         <v>8.9</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3482,7 +3399,6 @@
       <c r="D83" t="n">
         <v>6.9</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3514,7 +3430,6 @@
       <c r="D84" t="n">
         <v>8.9</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3546,7 +3461,6 @@
       <c r="D85" t="n">
         <v>11.9</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3578,7 +3492,6 @@
       <c r="D86" t="n">
         <v>7</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3610,7 +3523,6 @@
       <c r="D87" t="n">
         <v>4</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>pastry</t>
@@ -3642,7 +3554,6 @@
       <c r="D88" t="n">
         <v>12</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3674,7 +3585,6 @@
       <c r="D89" t="n">
         <v>12</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3706,7 +3616,6 @@
       <c r="D90" t="n">
         <v>13</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3738,7 +3647,6 @@
       <c r="D91" t="n">
         <v>8</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>fry</t>
@@ -3770,7 +3678,6 @@
       <c r="D92" t="n">
         <v>10</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3802,7 +3709,6 @@
       <c r="D93" t="n">
         <v>10</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3834,7 +3740,6 @@
       <c r="D94" t="n">
         <v>4</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3866,7 +3771,6 @@
       <c r="D95" t="n">
         <v>4</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3898,7 +3802,6 @@
       <c r="D96" t="n">
         <v>9</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3930,7 +3833,6 @@
       <c r="D97" t="n">
         <v>8</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>saute</t>
@@ -3962,7 +3864,6 @@
       <c r="D98" t="n">
         <v>3</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>pastry</t>
@@ -3994,7 +3895,6 @@
       <c r="D99" t="n">
         <v>7</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4026,7 +3926,6 @@
       <c r="D100" t="n">
         <v>8</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4058,7 +3957,6 @@
       <c r="D101" t="n">
         <v>8</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4090,7 +3988,6 @@
       <c r="D102" t="n">
         <v>8</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4122,7 +4019,6 @@
       <c r="D103" t="n">
         <v>8</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4154,7 +4050,6 @@
       <c r="D104" t="n">
         <v>3</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4186,7 +4081,6 @@
       <c r="D105" t="n">
         <v>2</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>saute</t>
@@ -4218,7 +4112,6 @@
       <c r="D106" t="n">
         <v>1.8</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4250,7 +4143,6 @@
       <c r="D107" t="n">
         <v>3</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4282,7 +4174,6 @@
       <c r="D108" t="n">
         <v>3.5</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4314,7 +4205,6 @@
       <c r="D109" t="n">
         <v>3.5</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4346,7 +4236,6 @@
       <c r="D110" t="n">
         <v>4</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4378,7 +4267,6 @@
       <c r="D111" t="n">
         <v>4</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4410,7 +4298,6 @@
       <c r="D112" t="n">
         <v>6</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4442,7 +4329,6 @@
       <c r="D113" t="n">
         <v>2.5</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4474,7 +4360,6 @@
       <c r="D114" t="n">
         <v>2.5</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4506,7 +4391,6 @@
       <c r="D115" t="n">
         <v>3.5</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4538,7 +4422,6 @@
       <c r="D116" t="n">
         <v>3.5</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4570,7 +4453,6 @@
       <c r="D117" t="n">
         <v>3</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4602,7 +4484,6 @@
       <c r="D118" t="n">
         <v>3</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4634,7 +4515,6 @@
       <c r="D119" t="n">
         <v>3</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4666,7 +4546,6 @@
       <c r="D120" t="n">
         <v>4</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4698,7 +4577,6 @@
       <c r="D121" t="n">
         <v>5</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4730,7 +4608,6 @@
       <c r="D122" t="n">
         <v>4.5</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>fry</t>
@@ -4762,7 +4639,6 @@
       <c r="D123" t="n">
         <v>2</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4794,7 +4670,6 @@
       <c r="D124" t="n">
         <v>2.5</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4826,7 +4701,6 @@
       <c r="D125" t="n">
         <v>3</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4858,7 +4732,6 @@
       <c r="D126" t="n">
         <v>2.5</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4890,7 +4763,6 @@
       <c r="D127" t="n">
         <v>2.5</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4922,7 +4794,6 @@
       <c r="D128" t="n">
         <v>2</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4954,7 +4825,6 @@
       <c r="D129" t="n">
         <v>2.5</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>bar</t>
@@ -4986,7 +4856,6 @@
       <c r="D130" t="n">
         <v>3</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5018,7 +4887,6 @@
       <c r="D131" t="n">
         <v>2</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5050,7 +4918,6 @@
       <c r="D132" t="n">
         <v>2.5</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5082,7 +4949,6 @@
       <c r="D133" t="n">
         <v>2.5</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5114,7 +4980,6 @@
       <c r="D134" t="n">
         <v>2</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5146,7 +5011,6 @@
       <c r="D135" t="n">
         <v>3</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5178,7 +5042,6 @@
       <c r="D136" t="n">
         <v>3</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5210,7 +5073,6 @@
       <c r="D137" t="n">
         <v>4</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5242,7 +5104,6 @@
       <c r="D138" t="n">
         <v>2.5</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5274,7 +5135,6 @@
       <c r="D139" t="n">
         <v>3</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5306,7 +5166,6 @@
       <c r="D140" t="n">
         <v>3.5</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5338,7 +5197,6 @@
       <c r="D141" t="n">
         <v>2.5</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5370,7 +5228,6 @@
       <c r="D142" t="n">
         <v>2.5</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5402,7 +5259,6 @@
       <c r="D143" t="n">
         <v>4</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5434,7 +5290,6 @@
       <c r="D144" t="n">
         <v>5.5</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5466,7 +5321,6 @@
       <c r="D145" t="n">
         <v>3.5</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5498,7 +5352,6 @@
       <c r="D146" t="n">
         <v>1.5</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>bar</t>
@@ -5530,7 +5383,6 @@
       <c r="D147" t="n">
         <v>2.5</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>bar</t>

--- a/menu/the-great-invention-menu.xlsx
+++ b/menu/the-great-invention-menu.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Suppliers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ingredients" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SubRecipes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BOM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Menu" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Allergens" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Staff" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ingredients" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SubRecipes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BOM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Menu" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Allergens" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,6 +626,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>hourly_rate</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>max_weekly_hours</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>min_rest_hours</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -700,7 +788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -760,7 +848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -808,7 +896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5400,7 +5488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
